--- a/PRs.xlsx
+++ b/PRs.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:O167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -440,7 +440,8 @@
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -501,15 +502,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Has Issue</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>AI Generated</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
@@ -562,10 +568,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>The PR optimizes the einsum algorithm by replacing tensordot calls with batched matrix multiplication, which is claimed to be a uniform improvement across all cases when optimize=True.</t>
         </is>
@@ -619,13 +630,18 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>The PR generalizes the existing hash-based unique implementation to support additional data types including strings, resulting in significant performance improvement without changing the mathematical output.</t>
         </is>
@@ -680,13 +696,18 @@
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>The PR fixes the incorrect implementation of using a rotated companion matrix in polynomial.polyroots, which was causing numerical instability.</t>
         </is>
@@ -747,10 +768,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the covariance and correlation coefficient estimation algorithms by optimizing data type usage and reducing unnecessary computations.</t>
         </is>
@@ -807,10 +833,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect handling of bins argument in histogram2d algorithm.</t>
         </is>
@@ -864,13 +895,18 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>The PR limits the maximum number of bins in automatic histogram binning using Sturges' rule, addressing a bug where the number of bins could become excessively large.</t>
         </is>
@@ -931,10 +967,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>The PR introduces an optimized version of quicksort using AVX512 instructions for 16-bit and 64-bit dtypes, which significantly improves the sorting speed.</t>
         </is>
@@ -991,10 +1032,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>The PR integrates Intel Short Vector Math Library (SVML) into NumPy, providing AVX-512 implementations for 44 mathematical functions, resulting in significant speed improvements without changing the mathematical output.</t>
         </is>
@@ -1051,10 +1097,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>The PR changes the computation of 'indices' for percentile and quantile methods, correcting the formula from 'q * (Nx - 1)' to '(q * Nx) - 1', which is a direct fix to the algorithm's implementation.</t>
         </is>
@@ -1111,10 +1162,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>The PR makes the window functions exactly symmetric by changing the cosine function's argument to ensure symmetry around zero, which is a correction to the implementation of these window functions.</t>
         </is>
@@ -1167,10 +1223,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>The PR introduces the use of a rotated companion matrix in root finding algorithms to reduce error, which is an improvement in the efficiency of the algorithm.</t>
         </is>
@@ -1223,10 +1284,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Optimizes the 'array_equal' function for the case where 'equal_nan=True' by using a single vectorized predicate and reduction, avoiding boolean masking and indexing.</t>
         </is>
@@ -1279,10 +1345,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>Optimized the computation of weighted quantiles by removing unnecessary stable sorting, improving efficiency without changing the mathematical output.</t>
         </is>
@@ -1343,10 +1414,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Reimplementation of the ndindex algorithm using itertools.product for performance and memory efficiency improvements.</t>
         </is>
@@ -1399,10 +1475,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>The change optimizes the evaluation of Legendre polynomials by combining two broadcasted scalar multiplies into one, resulting in a 30% runtime improvement.</t>
         </is>
@@ -1455,10 +1536,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Optimized the array_equal function to handle specific cases more efficiently without changing the underlying algorithm's mathematical output.</t>
         </is>
@@ -1512,13 +1598,18 @@
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>The PR fixes an issue with the einsum function where it fails with a 0-dimensional out argument and optimize='optimal'.</t>
         </is>
@@ -1572,13 +1663,18 @@
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>The PR fixes an issue with the np.einsum() function when used with a 0-dimensional out argument and optimize='optimal'.</t>
         </is>
@@ -1635,10 +1731,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>Optimized the performance of the np.atleast_1d function, which is a utility for ensuring arrays are at least one-dimensional.</t>
         </is>
@@ -1695,10 +1796,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Implements the analytical expression for linear interpolation consistent with de Boor's algorithm, fixing numerical stability issues in interp1d.</t>
         </is>
@@ -1755,10 +1861,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>Implements a new method for computing the Wasserstein distance using linear programming.</t>
         </is>
@@ -1822,10 +1933,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>Adds Whittaker-Henderson smoothing/graduation, a new algorithm to the scipy.signal module.</t>
         </is>
@@ -1879,13 +1995,18 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>This PR extends the Riemann Zeta function to complex inputs, which was not previously supported in the codebase.</t>
         </is>
@@ -1942,10 +2063,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect default bracket selection in the _bracket_minimum algorithm for scalar minimization.</t>
         </is>
@@ -2003,10 +2129,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>The PR adds nD batch support and structure detection to the matrix inversion algorithm in scipy.linalg.inv, improving efficiency.</t>
         </is>
@@ -2067,10 +2198,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>Implements a more efficient banded solver for linear systems in C++, removing the need for an additional 'solve0' function call.</t>
         </is>
@@ -2133,10 +2269,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="O28" s="3" t="inlineStr">
         <is>
           <t>Adds a new implementation of the Landau distribution, a special case of scipy.stats.levy_stable when alpha=beta=1.</t>
         </is>
@@ -2194,10 +2335,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>The PR adds support for n-dimensional batches of linear operators in `sparse.linalg.LinearOperator`, which is an API extension rather than a change to a specific named algorithm.</t>
         </is>
@@ -2259,10 +2405,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="O30" s="3" t="inlineStr">
         <is>
           <t>The PR improves the performance of the Singular Value Decomposition (SVD) algorithm by moving the batching loop to C, resulting in performance on par with np.linalg.svd.</t>
         </is>
@@ -2316,13 +2467,18 @@
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect handling of large assignments in CSR/CSC sparse matrices that could lead to a ValueError due to index array overflow.</t>
         </is>
@@ -2375,10 +2531,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="O32" s="3" t="inlineStr">
         <is>
           <t>The PR adds support for nd inputs to Minkowski, Euclidean, and Seuclidean distance functions, which are not changes to a specific algorithm but rather an extension of existing functionality.</t>
         </is>
@@ -2436,13 +2597,18 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>The PR improves the performance of the Cholesky decomposition algorithm by leveraging symmetry and avoiding unnecessary copies, resulting in a 2-5x speedup for real matrices.</t>
         </is>
@@ -2505,10 +2671,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="O34" s="3" t="inlineStr">
         <is>
           <t>The PR moves the batching loop of the Cholesky decomposition algorithm to C, improving performance for batched small matrices.</t>
         </is>
@@ -2564,13 +2735,18 @@
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>The PR changes the implementation of the ncfdtr algorithm to use a more accurate Boost implementation, fixing accuracy issues.</t>
         </is>
@@ -2624,13 +2800,18 @@
       <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="O36" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect PDF results in the far tails for the Levy Stable distribution when beta equals +-1.</t>
         </is>
@@ -2688,10 +2869,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="O37" s="3" t="inlineStr">
         <is>
           <t>Reimplementation of the Shapiro-Wilk test in Python array API/NumPy for potential vectorization benefits and future translation to array API.</t>
         </is>
@@ -2752,10 +2938,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N38" s="3" t="inlineStr">
+      <c r="O38" s="3" t="inlineStr">
         <is>
           <t>Adds a new method to compute population L-moments for continuous distributions in scipy.stats.</t>
         </is>
@@ -2809,13 +3000,18 @@
       <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="O39" s="3" t="inlineStr">
         <is>
           <t>Refactored the calculation of initial filter coefficients for the lfilter algorithm to be more efficient and numerically stable.</t>
         </is>
@@ -2868,10 +3064,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N40" s="3" t="inlineStr">
+      <c r="O40" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the Hilbert transform algorithm by avoiding extra scaling array allocation and adding batched 2D transform support.</t>
         </is>
@@ -2936,10 +3137,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="3" t="inlineStr">
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>Adds the matrix variate t distribution, a new statistical distribution to scipy.stats.</t>
         </is>
@@ -3000,10 +3206,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N42" s="3" t="inlineStr">
+      <c r="O42" s="3" t="inlineStr">
         <is>
           <t>The PR adds xp_capabilities for scipy.signal functions and updates tests, but does not introduce or modify a specific named algorithm.</t>
         </is>
@@ -3065,10 +3276,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="3" t="inlineStr">
+      <c r="O43" s="3" t="inlineStr">
         <is>
           <t>Adds a new function to compute Sobol' indices, a recognized sensitivity analysis method.</t>
         </is>
@@ -3125,10 +3341,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n">
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N44" s="3" t="inlineStr">
+      <c r="O44" s="3" t="inlineStr">
         <is>
           <t>The PR vectorizes the implementation of Mood's median test, which is expected to improve efficiency without changing the algorithm's mathematical output.</t>
         </is>
@@ -3185,10 +3406,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n">
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N45" s="3" t="inlineStr">
+      <c r="O45" s="3" t="inlineStr">
         <is>
           <t>Refactored the 'Rotation' class into a pure Python class with a Cython backend to improve efficiency for numpy arrays.</t>
         </is>
@@ -3246,10 +3472,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="3" t="inlineStr">
+      <c r="O46" s="3" t="inlineStr">
         <is>
           <t>Adds the binomial distribution as `scipy.stats.Binomial` using a new infrastructure for discrete distributions.</t>
         </is>
@@ -3306,10 +3537,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n">
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="3" t="inlineStr">
+      <c r="O47" s="3" t="inlineStr">
         <is>
           <t>Adds a new Quasi-Monte Carlo module with various samplers including Sobol, Halton, Latin Hypercube, and more.</t>
         </is>
@@ -3370,10 +3606,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n">
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N48" s="3" t="inlineStr">
+      <c r="O48" s="3" t="inlineStr">
         <is>
           <t>Adds bounds parameters to Poisson Disk Sampling algorithm to allow for equal scaling in target sample.</t>
         </is>
@@ -3430,10 +3671,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n">
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N49" s="3" t="inlineStr">
+      <c r="O49" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the 1D rank filter algorithm by reducing its time complexity from O(n) to O(log n).</t>
         </is>
@@ -3494,10 +3740,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n">
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N50" s="3" t="inlineStr">
+      <c r="O50" s="3" t="inlineStr">
         <is>
           <t>Implements the generalized Lomb-Scargle periodogram, which is an enhancement of the existing algorithm with additional functionality for sample weights and correctly removing unknown y offset.</t>
         </is>
@@ -3558,10 +3809,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n">
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N51" s="3" t="inlineStr">
+      <c r="O51" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the entropy calculation for discrete distributions by ensuring the summand is always negative, which allows `nsum` to rely on the integral for the remainder instead of evaluating too many terms directly.</t>
         </is>
@@ -3618,10 +3874,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n">
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="3" t="inlineStr">
+      <c r="O52" s="3" t="inlineStr">
         <is>
           <t>Fixes the K-means clustering algorithm to ensure the distortion value returned corresponds to the final codebook after centroid updates and empty-cluster removal.</t>
         </is>
@@ -3678,13 +3939,18 @@
       <c r="K53" s="3" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr">
         <is>
           <t>The PR fixes the trapezoid algorithm's convergence issue by changing the default parameters for `c` and `d`.</t>
         </is>
@@ -3739,13 +4005,18 @@
       <c r="K54" s="3" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N54" s="3" t="inlineStr">
+      <c r="O54" s="3" t="inlineStr">
         <is>
           <t>Implements a new restarted Krylov method for computing f(A)b for an arbitrary function f and vector b.</t>
         </is>
@@ -3802,10 +4073,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n">
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N55" s="3" t="inlineStr">
+      <c r="O55" s="3" t="inlineStr">
         <is>
           <t>Adds Lebedev quadrature, a new numerical integration method for functions on the sphere.</t>
         </is>
@@ -3863,10 +4139,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n">
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="3" t="inlineStr">
+      <c r="O56" s="3" t="inlineStr">
         <is>
           <t>Adds a new RigidTransform class for representing and manipulating 3D rotations and translations, which is a new named scientific algorithm.</t>
         </is>
@@ -3926,10 +4207,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n">
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N57" s="3" t="inlineStr">
+      <c r="O57" s="3" t="inlineStr">
         <is>
           <t>The PR implements a more efficient calculation for the noncentral moments of the halfgennorm distribution by using a formula instead of numerical integration.</t>
         </is>
@@ -3988,10 +4274,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M58" s="2" t="n">
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N58" s="3" t="inlineStr">
+      <c r="O58" s="3" t="inlineStr">
         <is>
           <t>The PR fixes a bug in the `rankdata` algorithm where `_rankdata` was not returning the expected number of outputs.</t>
         </is>
@@ -4048,10 +4339,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n">
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N59" s="3" t="inlineStr">
+      <c r="O59" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect enforcement of constraint feasibility in the trust-constr optimization algorithm.</t>
         </is>
@@ -4109,10 +4405,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n">
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="N60" s="3" t="inlineStr">
+      <c r="O60" s="3" t="inlineStr">
         <is>
           <t>Fixes numerical instability in the power mean algorithm for small but finite p values by using a linearized approximation.</t>
         </is>
@@ -4169,10 +4470,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n">
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N61" s="3" t="inlineStr">
+      <c r="O61" s="3" t="inlineStr">
         <is>
           <t>Fixes precision loss/overflow in the Yeo-Johnson log-likelihood formula.</t>
         </is>
@@ -4230,10 +4536,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M62" s="2" t="n">
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N62" s="3" t="inlineStr">
+      <c r="O62" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect index computation in the ShortTimeFFT algorithm.</t>
         </is>
@@ -4291,10 +4602,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M63" s="2" t="n">
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N63" s="3" t="inlineStr">
+      <c r="O63" s="3" t="inlineStr">
         <is>
           <t>The PR updates the `least_squares` algorithm to use `VectorFunction` for calculating numeric derivatives, which is more accurate and offers additional features like parallelization and different step methods.</t>
         </is>
@@ -4352,10 +4668,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n">
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N64" s="3" t="inlineStr">
+      <c r="O64" s="3" t="inlineStr">
         <is>
           <t>Adds parallelisation of numerical differentiation during Jacobian estimation in the least_squares algorithm.</t>
         </is>
@@ -4417,10 +4738,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n">
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N65" s="3" t="inlineStr">
+      <c r="O65" s="3" t="inlineStr">
         <is>
           <t>The PR moves the batching loop of the QR decomposition algorithm from Python to C, resulting in a significant speedup.</t>
         </is>
@@ -4481,10 +4807,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n">
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N66" s="3" t="inlineStr">
+      <c r="O66" s="3" t="inlineStr">
         <is>
           <t>The PR moves the 'sym' and 'her' modes of 'linalg.solve' to C, similar to the 'inv' method, which involves using Cholesky decomposition for efficiency.</t>
         </is>
@@ -4541,10 +4872,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M67" s="2" t="n">
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N67" s="3" t="inlineStr">
+      <c r="O67" s="3" t="inlineStr">
         <is>
           <t>The PR optimizes the matrix to quaternion conversion algorithm by factoring out orthogonalization for known orthogonal matrices, skipping expensive checks and SVD when applicable.</t>
         </is>
@@ -4602,10 +4938,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M68" s="2" t="n">
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N68" s="3" t="inlineStr">
+      <c r="O68" s="3" t="inlineStr">
         <is>
           <t>Implements the RigidTransform.mean() algorithm, which calculates the mean of a set of rigid transformations.</t>
         </is>
@@ -4662,10 +5003,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M69" s="2" t="n">
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N69" s="3" t="inlineStr">
+      <c r="O69" s="3" t="inlineStr">
         <is>
           <t>Introduces a new function `estimated_cdf` (referred to as `ogive`) that implements functionality similar to `stats.mstats.plotting_positions`, `stats.percentileofscore`, `stats.ecdf.cdf`, and `stats.cumfreq`.</t>
         </is>
@@ -4726,10 +5072,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M70" s="2" t="n">
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N70" s="3" t="inlineStr">
+      <c r="O70" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the tridiagonal solve algorithm by converting the slice iteration to C, resulting in significant speed-ups for deep batches of small matrices.</t>
         </is>
@@ -4791,10 +5142,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M71" s="2" t="n">
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N71" s="3" t="inlineStr">
+      <c r="O71" s="3" t="inlineStr">
         <is>
           <t>The PR moves the Linear Least Squares LAPACK wrappers from Python to C, improving efficiency by reducing the overhead of the Python loop.</t>
         </is>
@@ -4851,10 +5207,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M72" s="2" t="n">
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N72" s="3" t="inlineStr">
+      <c r="O72" s="3" t="inlineStr">
         <is>
           <t>The PR implements a direct and efficient conversion from DIA format to CSR format, which speeds up operations that require conversion to other formats.</t>
         </is>
@@ -4915,10 +5276,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M73" s="2" t="n">
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N73" s="3" t="inlineStr">
+      <c r="O73" s="3" t="inlineStr">
         <is>
           <t>The PR implements an optimized version of the bivariate normal cumulative distribution function (CDF), resulting in a significant speed improvement without changing the mathematical output.</t>
         </is>
@@ -4971,10 +5337,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M74" s="2" t="n">
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N74" s="3" t="inlineStr">
+      <c r="O74" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the quantile computation algorithm by changing the sort to be non-stable, which is 6-9x faster and does not affect the correctness of the quantile result.</t>
         </is>
@@ -5031,10 +5402,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M75" s="2" t="n">
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N75" s="3" t="inlineStr">
+      <c r="O75" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the array_namespace function by 4x to 8x for numpy arrays and array-likes, and 1.4x for other Array API objects through caching.</t>
         </is>
@@ -5088,13 +5464,18 @@
       <c r="K76" s="3" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N76" s="3" t="inlineStr">
+      <c r="O76" s="3" t="inlineStr">
         <is>
           <t>The PR updates the implementation of the noncentral T distribution PDF to address accuracy issues in the left tail using Boost.</t>
         </is>
@@ -5156,10 +5537,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M77" s="2" t="n">
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N77" s="3" t="inlineStr">
+      <c r="O77" s="3" t="inlineStr">
         <is>
           <t>Implements a new multidimensional integration algorithm called 'cubature' for array-valued functions.</t>
         </is>
@@ -5214,13 +5600,18 @@
       <c r="K78" s="3" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N78" s="3" t="inlineStr">
+      <c r="O78" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect handling of datetime64 and timedelta64 dtypes in the covariance calculation.</t>
         </is>
@@ -5279,13 +5670,18 @@
       <c r="K79" s="3" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N79" s="3" t="inlineStr">
+      <c r="O79" s="3" t="inlineStr">
         <is>
           <t>Fixes a bug with incorrect min/max rolling calculation for custom window sizes and adds error checks for invalid inputs.</t>
         </is>
@@ -5339,13 +5735,18 @@
       <c r="K80" s="3" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N80" s="3" t="inlineStr">
+      <c r="O80" s="3" t="inlineStr">
         <is>
           <t>Optimized the 'nlargest' algorithm to handle duplicate indices more efficiently, improving performance.</t>
         </is>
@@ -5407,10 +5808,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M81" s="2" t="n">
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N81" s="3" t="inlineStr">
+      <c r="O81" s="3" t="inlineStr">
         <is>
           <t>Optimizes datetimelike addition by replacing checked_add_with_arr with add_overflowsafe for better performance.</t>
         </is>
@@ -5465,13 +5871,18 @@
       <c r="K82" s="3" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N82" s="3" t="inlineStr">
+      <c r="O82" s="3" t="inlineStr">
         <is>
           <t>Implements a new masked mode algorithm to handle missing data in the mode computation.</t>
         </is>
@@ -5524,10 +5935,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M83" s="2" t="n">
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N83" s="3" t="inlineStr">
+      <c r="O83" s="3" t="inlineStr">
         <is>
           <t>Fixes out-of-bounds access in kth_smallest algorithm when n &lt;= 0.</t>
         </is>
@@ -5585,10 +6001,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M84" s="2" t="n">
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N84" s="3" t="inlineStr">
+      <c r="O84" s="3" t="inlineStr">
         <is>
           <t>Implements a masked algorithm for value_counts to improve performance with growing numbers of NAs.</t>
         </is>
@@ -5645,10 +6066,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M85" s="2" t="n">
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N85" s="3" t="inlineStr">
+      <c r="O85" s="3" t="inlineStr">
         <is>
           <t>Optimizes the 'take' algorithm by caching expensive parts and adding a specialized version for 1D arrays, resulting in performance improvements without changing the algorithm's output.</t>
         </is>
@@ -5702,13 +6128,18 @@
       <c r="K86" s="3" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N86" s="3" t="inlineStr">
+      <c r="O86" s="3" t="inlineStr">
         <is>
           <t>The PR optimizes the lexsort_indexer function by skipping unnecessary Categorical conversion for numeric types and directly passing values to np.lexsort, resulting in a ~3x speedup for multi-column DataFrame.sort_values on numeric DataFrames.</t>
         </is>
@@ -5767,13 +6198,18 @@
       <c r="K87" s="3" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N87" s="3" t="inlineStr">
+      <c r="O87" s="3" t="inlineStr">
         <is>
           <t>Implements a new algorithm for weighted rolling variance and standard deviation based on West's algorithm.</t>
         </is>
@@ -5834,10 +6270,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M88" s="2" t="n">
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N88" s="3" t="inlineStr">
+      <c r="O88" s="3" t="inlineStr">
         <is>
           <t>Implements a modified version of Welford's method to compute rolling variance, improving numerical stability.</t>
         </is>
@@ -5895,10 +6336,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M89" s="2" t="n">
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N89" s="3" t="inlineStr">
+      <c r="O89" s="3" t="inlineStr">
         <is>
           <t>Adds support for melting MultiIndex DataFrames with col_level parameter in the melt function.</t>
         </is>
@@ -5951,10 +6397,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M90" s="2" t="n">
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N90" s="3" t="inlineStr">
+      <c r="O90" s="3" t="inlineStr">
         <is>
           <t>Replaced pandas' unique algorithm with numpy's unique algorithm to improve performance on simple int32/int64 numpy arrays.</t>
         </is>
@@ -6016,10 +6467,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M91" s="2" t="n">
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N91" s="3" t="inlineStr">
+      <c r="O91" s="3" t="inlineStr">
         <is>
           <t>The PR introduces a Cythonized implementation of the GroupBy `quantile` function, which is a specific scientific algorithm, resulting in significant performance improvements as shown in the ASV benchmarks.</t>
         </is>
@@ -6076,13 +6532,18 @@
       <c r="K92" s="3" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N92" s="3" t="inlineStr">
+      <c r="O92" s="3" t="inlineStr">
         <is>
           <t>The PR fixes an issue with the time series interpolation method in pandas, ensuring that all available datapoints from the original series become anchors for interpolation.</t>
         </is>
@@ -6143,10 +6604,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M93" s="2" t="n">
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N93" s="3" t="inlineStr">
+      <c r="O93" s="3" t="inlineStr">
         <is>
           <t>Implements hash_join for merges, improving time complexity from O(m*n) to O(m+n).</t>
         </is>
@@ -6196,13 +6662,18 @@
       <c r="K94" s="3" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N94" s="3" t="inlineStr">
+      <c r="O94" s="3" t="inlineStr">
         <is>
           <t>Optimizes the generation of business day ranges by vectorizing the filtering process instead of applying the offset iteratively, resulting in significant performance improvements for BusinessDay and CustomBusinessDay.</t>
         </is>
@@ -6260,10 +6731,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M95" s="2" t="n">
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N95" s="3" t="inlineStr">
+      <c r="O95" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of IntervalIndex.get_indexer for monotonic indexes by using searchsorted instead of IntervalTree, resulting in a significant speedup.</t>
         </is>
@@ -6313,13 +6789,18 @@
       <c r="K96" s="3" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N96" s="3" t="inlineStr">
+      <c r="O96" s="3" t="inlineStr">
         <is>
           <t>Improves the efficiency of hashing for IntervalArray categories by ~33x, using native _hash_pandas_object instead of string-conversion fallback.</t>
         </is>
@@ -6372,10 +6853,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M97" s="2" t="n">
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N97" s="3" t="inlineStr">
+      <c r="O97" s="3" t="inlineStr">
         <is>
           <t>Optimizes StringDtype arrow implementation for merge to run faster without changing the algorithm's output.</t>
         </is>
@@ -6429,13 +6915,18 @@
       <c r="K98" s="3" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N98" s="3" t="inlineStr">
+      <c r="O98" s="3" t="inlineStr">
         <is>
           <t>Fixes a ValueError in KNeighborsClassifier with brute force and p=1 by passing integer indices instead of string labels to the Cython method.</t>
         </is>
@@ -6490,13 +6981,18 @@
       <c r="K99" s="3" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N99" s="3" t="inlineStr">
+      <c r="O99" s="3" t="inlineStr">
         <is>
           <t>Optimized the call to `eigsh()` in spectral embedding, resulting in faster computation.</t>
         </is>
@@ -6549,10 +7045,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M100" s="2" t="n">
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N100" s="3" t="inlineStr">
+      <c r="O100" s="3" t="inlineStr">
         <is>
           <t>Optimized the `_logcosh` function in FastICA for 1D arrays by vectorizing operations, resulting in a significant speedup.</t>
         </is>
@@ -6609,10 +7110,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M101" s="2" t="n">
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N101" s="3" t="inlineStr">
+      <c r="O101" s="3" t="inlineStr">
         <is>
           <t>Fixed a bug in BisectingKMeans where the validation logic incorrectly checked the shape of custom init centroids.</t>
         </is>
@@ -6662,13 +7168,18 @@
       <c r="K102" s="3" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N102" s="3" t="inlineStr">
+      <c r="O102" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect handling of sample weights in the MinibatchKMeans algorithm.</t>
         </is>
@@ -6728,10 +7239,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M103" s="2" t="n">
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N103" s="3" t="inlineStr">
+      <c r="O103" s="3" t="inlineStr">
         <is>
           <t>Implements gap safe screening rules in the Elastic Net algorithm to improve efficiency.</t>
         </is>
@@ -6786,13 +7302,18 @@
       <c r="K104" s="3" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N104" s="3" t="inlineStr">
+      <c r="O104" s="3" t="inlineStr">
         <is>
           <t>Corrects the convergence criteria for SGD models to use the full objective value instead of raw error, affecting SGDRegressor, SGDClassifier, and SGDOneClassSVM.</t>
         </is>
@@ -6850,13 +7371,18 @@
       <c r="K105" s="3" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N105" s="3" t="inlineStr">
+      <c r="O105" s="3" t="inlineStr">
         <is>
           <t>Implements a new algorithm, Classical MDS, also known as principal coordinates analysis (PCoA) or Torgerson's scaling.</t>
         </is>
@@ -6912,13 +7438,18 @@
       <c r="K106" s="3" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N106" s="3" t="inlineStr">
+      <c r="O106" s="3" t="inlineStr">
         <is>
           <t>The PR changes the implementation of the SparseCoder algorithm to correctly run common estimator tests, including modifying attributes and validation behavior.</t>
         </is>
@@ -6980,10 +7511,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M107" s="2" t="n">
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N107" s="3" t="inlineStr">
+      <c r="O107" s="3" t="inlineStr">
         <is>
           <t>Implements Gap Safe Screening Rules to speed up the enet_coordinate_descent algorithm as referenced in the paper.</t>
         </is>
@@ -7040,10 +7576,15 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M108" s="2" t="n">
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N108" s="3" t="inlineStr">
+      <c r="O108" s="3" t="inlineStr">
         <is>
           <t>Fixes an incorrect implementation of the euclidean_distances algorithm where Y_norm_squared was not sliced alongside Y for parallel execution.</t>
         </is>
@@ -7097,13 +7638,18 @@
       <c r="K109" s="3" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N109" s="3" t="inlineStr">
+      <c r="O109" s="3" t="inlineStr">
         <is>
           <t>Fixes an overflow issue in the RidgeClassifier label binarisation, which is a part of the algorithm's implementation.</t>
         </is>
@@ -7161,13 +7707,18 @@
       <c r="K110" s="3" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N110" s="3" t="inlineStr">
+      <c r="O110" s="3" t="inlineStr">
         <is>
           <t>The PR fixes the bias in the MinCovDet algorithm by adding a missing consistency correction as described in the referenced paper.</t>
         </is>
@@ -7228,10 +7779,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M111" s="2" t="n">
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N111" s="3" t="inlineStr">
+      <c r="O111" s="3" t="inlineStr">
         <is>
           <t>Refactored _average_weighted_percentile to avoid double sorting and computing cumulative sum twice, improving efficiency of the _weighted_percentile algorithm.</t>
         </is>
@@ -7285,13 +7841,18 @@
       <c r="K112" s="3" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M112" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N112" s="3" t="inlineStr">
+      <c r="O112" s="3" t="inlineStr">
         <is>
           <t>Fixes severe implementation errors in non-metric MDS, including incorrect copying of disparities matrix and incorrect execution order of isotonic regression and SMACOF update.</t>
         </is>
@@ -7349,13 +7910,18 @@
       <c r="K113" s="3" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M113" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N113" s="3" t="inlineStr">
+      <c r="O113" s="3" t="inlineStr">
         <is>
           <t>Implements the Stress-1 algorithm for the `smacof` algorithm in `manifold.MDS`.</t>
         </is>
@@ -7409,13 +7975,18 @@
       <c r="K114" s="3" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M114" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N114" s="3" t="inlineStr">
+      <c r="O114" s="3" t="inlineStr">
         <is>
           <t>Adds decision_function, predict_proba, and predict_log_proba methods to the NearestCentroid estimator, implementing the NearestCentroid algorithm with class priors.</t>
         </is>
@@ -7472,10 +8043,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M115" s="2" t="n">
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N115" s="3" t="inlineStr">
+      <c r="O115" s="3" t="inlineStr">
         <is>
           <t>The PR fixes an incorrect implementation in RidgeCV where the predictions were computed in a scaled space instead of the original space for arbitrary scorer metrics.</t>
         </is>
@@ -7525,13 +8101,18 @@
       <c r="K116" s="3" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M116" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N116" s="3" t="inlineStr">
+      <c r="O116" s="3" t="inlineStr">
         <is>
           <t>Fixes the ConvergenceWarning and L-BFGS abort in Gaussian Process Regression by freezing `baseline_similarity_bounds`.</t>
         </is>
@@ -7589,10 +8170,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M117" s="2" t="n">
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N117" s="3" t="inlineStr">
+      <c r="O117" s="3" t="inlineStr">
         <is>
           <t>Adds array API support to PoissonRegressor with LBFGS solver, enabling the use of this regression algorithm with array APIs.</t>
         </is>
@@ -7646,13 +8232,18 @@
       <c r="K118" s="3" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M118" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N118" s="3" t="inlineStr">
+      <c r="O118" s="3" t="inlineStr">
         <is>
           <t>Fixes LogisticRegressionCV to handle CV folds with missing class labels correctly.</t>
         </is>
@@ -7706,13 +8297,18 @@
       <c r="K119" s="3" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M119" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N119" s="3" t="inlineStr">
+      <c r="O119" s="3" t="inlineStr">
         <is>
           <t>Fixes numerical errors in the small alpha regime for Ridge Regression by refactoring the solve/decompose methods.</t>
         </is>
@@ -7770,10 +8366,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M120" s="2" t="n">
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N120" s="3" t="inlineStr">
+      <c r="O120" s="3" t="inlineStr">
         <is>
           <t>The PR fixes the convergence issue of the coordinate descent solver for Ridge regression when alpha=0 or l1_ratio=0.</t>
         </is>
@@ -7830,10 +8431,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M121" s="2" t="n">
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N121" s="3" t="inlineStr">
+      <c r="O121" s="3" t="inlineStr">
         <is>
           <t>Corrects the formulation of `alpha` in `SGDOneClassSVM` by using `alpha = nu` instead of `alpha = nu / 2`.</t>
         </is>
@@ -7893,10 +8499,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M122" s="2" t="n">
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N122" s="3" t="inlineStr">
+      <c r="O122" s="3" t="inlineStr">
         <is>
           <t>The PR changes the stopping criterion from 'gap &lt; tol' to 'gap &lt;= tol' in the Coordinate Descent algorithm.</t>
         </is>
@@ -7950,13 +8561,18 @@
       <c r="K123" s="3" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M123" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N123" s="3" t="inlineStr">
+      <c r="O123" s="3" t="inlineStr">
         <is>
           <t>Adds temperature scaling, a new calibration method for CalibratedClassifierCV.</t>
         </is>
@@ -8009,10 +8625,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M124" s="2" t="n">
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N124" s="3" t="inlineStr">
+      <c r="O124" s="3" t="inlineStr">
         <is>
           <t>Changed the epsilon value used in clipping initial probabilities for the Gradient Boosting algorithm to match the float64 precision used later.</t>
         </is>
@@ -8070,10 +8691,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M125" s="2" t="n">
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N125" s="3" t="inlineStr">
+      <c r="O125" s="3" t="inlineStr">
         <is>
           <t>The PR fixes a wrong implementation in the L-BFGS-B optimization algorithm by correctly handling the maximum number of iterations.</t>
         </is>
@@ -8131,10 +8757,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M126" s="2" t="n">
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N126" s="3" t="inlineStr">
+      <c r="O126" s="3" t="inlineStr">
         <is>
           <t>Changed the default parameters for the MDS algorithm to align with the R implementation and to fix issues with convergence and underconvergence.</t>
         </is>
@@ -8190,13 +8821,18 @@
       <c r="K127" s="3" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N127" s="3" t="inlineStr">
+      <c r="O127" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect handling of mixed string and number inputs for thresholded classification metrics.</t>
         </is>
@@ -8253,10 +8889,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M128" s="2" t="n">
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N128" s="3" t="inlineStr">
+      <c r="O128" s="3" t="inlineStr">
         <is>
           <t>Replaces the incorrect custom implementation of the Yeo-Johnson transformation with the correct one from scipy.stats.yeojohnson.</t>
         </is>
@@ -8309,10 +8950,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M129" s="2" t="n">
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N129" s="3" t="inlineStr">
+      <c r="O129" s="3" t="inlineStr">
         <is>
           <t>Fixes type promotion mismatch in the log_loss algorithm.</t>
         </is>
@@ -8365,10 +9011,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M130" s="2" t="n">
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N130" s="3" t="inlineStr">
+      <c r="O130" s="3" t="inlineStr">
         <is>
           <t>The PR changes the PCA implementation to use more efficient array operations from the Array API, replacing the custom stable_cumsum function.</t>
         </is>
@@ -8422,13 +9073,18 @@
       <c r="K131" s="3" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M131" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N131" s="3" t="inlineStr">
+      <c r="O131" s="3" t="inlineStr">
         <is>
           <t>The PR modifies the Yeo-Johnson inverse transform to handle NaNs in extremely skewed data by changing the error state from 'ignore' to 'warn' and adding a warning for invalid values.</t>
         </is>
@@ -8481,10 +9137,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M132" s="2" t="n">
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N132" s="3" t="inlineStr">
+      <c r="O132" s="3" t="inlineStr">
         <is>
           <t>The PR avoids double input validation in ElasticNet and Lasso algorithms, which improves efficiency without changing the algorithms' mathematical output.</t>
         </is>
@@ -8542,10 +9203,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M133" s="2" t="n">
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N133" s="3" t="inlineStr">
+      <c r="O133" s="3" t="inlineStr">
         <is>
           <t>The PR uses Cython Tempita to generate Cython code from a template, reducing repeating code patterns for loops over samples in loss functions to guarantee inlining.</t>
         </is>
@@ -8600,13 +9266,18 @@
       <c r="K134" s="3" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M134" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N134" s="3" t="inlineStr">
+      <c r="O134" s="3" t="inlineStr">
         <is>
           <t>The PR replaces the loss functions used in the gradient boosting algorithm with a common private loss submodule, which is a change aimed at improving efficiency without altering the core algorithm's mathematical output.</t>
         </is>
@@ -8660,13 +9331,18 @@
       <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M135" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N135" s="3" t="inlineStr">
+      <c r="O135" s="3" t="inlineStr">
         <is>
           <t>Adds a new method to expose the latent mean and variance for binary Gaussian Process Classifiers.</t>
         </is>
@@ -8724,10 +9400,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M136" s="2" t="n">
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N136" s="3" t="inlineStr">
+      <c r="O136" s="3" t="inlineStr">
         <is>
           <t>Implements a new feature to enforce monotonicity constraints on tree-based models.</t>
         </is>
@@ -8780,13 +9461,18 @@
       <c r="K137" s="3" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M137" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N137" s="3" t="inlineStr">
+      <c r="O137" s="3" t="inlineStr">
         <is>
           <t>The PR simplifies the logic for handling missing values in tree-based estimators, specifically for MAE trees, by moving the responsibility from the Criterion subclasses to the splitter and partitionner, which improves efficiency without changing the algorithm's output.</t>
         </is>
@@ -8838,13 +9524,18 @@
       <c r="K138" s="3" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M138" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N138" s="3" t="inlineStr">
+      <c r="O138" s="3" t="inlineStr">
         <is>
           <t>The PR fixes the handling of sample weights in the BinMapper algorithm, which is a part of the HGBT (Histogram Gradient Boosting Trees) implementation.</t>
         </is>
@@ -8897,10 +9588,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M139" s="2" t="n">
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N139" s="3" t="inlineStr">
+      <c r="O139" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of Gaussian Process Regression by caching the `inspect.signature` calls within the kernels, which are a part of the GPR algorithm.</t>
         </is>
@@ -8953,10 +9649,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M140" s="2" t="n">
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N140" s="3" t="inlineStr">
+      <c r="O140" s="3" t="inlineStr">
         <is>
           <t>The PR changes the sorting algorithm in _weighted_percentile from stable to unstable sort, which is faster and does not affect the correctness of the weighted percentile computation.</t>
         </is>
@@ -9009,10 +9710,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M141" s="2" t="n">
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N141" s="3" t="inlineStr">
+      <c r="O141" s="3" t="inlineStr">
         <is>
           <t>The PR changes the kmeans++ initialization method to use np.cumsum instead of stable_cumsum, aiming to improve efficiency without altering the algorithm's output.</t>
         </is>
@@ -9069,10 +9775,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M142" s="2" t="n">
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N142" s="3" t="inlineStr">
+      <c r="O142" s="3" t="inlineStr">
         <is>
           <t>Ensures floating-point precision propagation in GaussianMixture, potentially improving numerical stability and efficiency.</t>
         </is>
@@ -9125,10 +9836,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M143" s="2" t="n">
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N143" s="3" t="inlineStr">
+      <c r="O143" s="3" t="inlineStr">
         <is>
           <t>Adds an 'eigh' solver to FastICA, improving efficiency when num_samples is much greater than num_features.</t>
         </is>
@@ -9181,10 +9897,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M144" s="2" t="n">
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N144" s="3" t="inlineStr">
+      <c r="O144" s="3" t="inlineStr">
         <is>
           <t>Optimized MinCovDet algorithm by reducing unnecessary sorting and conversions, resulting in a ~15% speedup.</t>
         </is>
@@ -9245,10 +9966,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M145" s="2" t="n">
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N145" s="3" t="inlineStr">
+      <c r="O145" s="3" t="inlineStr">
         <is>
           <t>The PR implements parallel computation for the Isolation Forest algorithm, allowing for improved efficiency in prediction.</t>
         </is>
@@ -9302,13 +10028,18 @@
       <c r="K146" s="3" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M146" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N146" s="3" t="inlineStr">
+      <c r="O146" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the classification_report function by attaching unique values to dtype.metadata, achieving the same speedup as a previous PR without modifying the underlying algorithm.</t>
         </is>
@@ -9361,10 +10092,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M147" s="2" t="n">
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N147" s="3" t="inlineStr">
+      <c r="O147" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the QuantileTransformer algorithm by removing the for-loop and transposing while computing the quantiles.</t>
         </is>
@@ -9419,13 +10155,18 @@
       <c r="K148" s="3" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M148" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N148" s="3" t="inlineStr">
+      <c r="O148" s="3" t="inlineStr">
         <is>
           <t>Implements a new PairwiseDistancesReduction backend algorithm for KNeighbors.predict.</t>
         </is>
@@ -9483,10 +10224,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M149" s="2" t="n">
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N149" s="3" t="inlineStr">
+      <c r="O149" s="3" t="inlineStr">
         <is>
           <t>The PR implements implicit mean centering to allow fitting PCA on sparse data without densifying the whole data matrix, which is a performance improvement for PCA.</t>
         </is>
@@ -9543,10 +10289,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M150" s="2" t="n">
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N150" s="3" t="inlineStr">
+      <c r="O150" s="3" t="inlineStr">
         <is>
           <t>Adds Array API support for d2_pinball_score, which is a new implementation of the D^2 score algorithm in the library.</t>
         </is>
@@ -9603,10 +10354,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M151" s="2" t="n">
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N151" s="3" t="inlineStr">
+      <c r="O151" s="3" t="inlineStr">
         <is>
           <t>The PR improves the efficiency of the _weighted_percentile algorithm by allowing it to handle multiple percentile ranks in a single call, reducing the need for repeated sorting.</t>
         </is>
@@ -9660,13 +10416,18 @@
       <c r="K152" s="3" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M152" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N152" s="3" t="inlineStr">
+      <c r="O152" s="3" t="inlineStr">
         <is>
           <t>The PR fixes the incorrect behavior of the GaussianProcessRegressor where the default kernel's hyperparameters were not being optimized when an optimizer was specified.</t>
         </is>
@@ -9720,13 +10481,18 @@
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M153" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N153" s="3" t="inlineStr">
+      <c r="O153" s="3" t="inlineStr">
         <is>
           <t>Fixes a ValueError in the Elastic Net algorithm's enet_path function when check_input is False.</t>
         </is>
@@ -9783,13 +10549,18 @@
       <c r="K154" s="3" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M154" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N154" s="3" t="inlineStr">
+      <c r="O154" s="3" t="inlineStr">
         <is>
           <t>The PR fixes the incorrect handling of sample_weight when subsampling is activated in Random Forest estimators.</t>
         </is>
@@ -9846,10 +10617,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M155" s="2" t="n">
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N155" s="3" t="inlineStr">
+      <c r="O155" s="3" t="inlineStr">
         <is>
           <t>Removed unnecessary max_features limit for SelectFromModel, allowing for more flexible hyperparameter optimization.</t>
         </is>
@@ -9906,10 +10682,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M156" s="2" t="n">
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N156" s="3" t="inlineStr">
+      <c r="O156" s="3" t="inlineStr">
         <is>
           <t>The PR updates the implementation of monotonic trees to correctly handle missing values, which was a previous limitation.</t>
         </is>
@@ -9963,10 +10744,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M157" s="2" t="n">
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="N157" s="3" t="inlineStr">
+      <c r="O157" s="3" t="inlineStr">
         <is>
           <t>The PR moves bitset Cython code to sklearn.utils, making it accessible and reusable from other submodules, but does not change any specific scientific algorithm.</t>
         </is>
@@ -10023,10 +10809,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M158" s="2" t="n">
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N158" s="3" t="inlineStr">
+      <c r="O158" s="3" t="inlineStr">
         <is>
           <t>Fixes sign handling in SVD when hermitian=True to ensure unitary vh when eigenvalues are zero.</t>
         </is>
@@ -10079,10 +10870,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M159" s="2" t="n">
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N159" s="3" t="inlineStr">
+      <c r="O159" s="3" t="inlineStr">
         <is>
           <t>Reduces memory pressure and redundant computations in the bivariate smoothing spline regression via regridding (_regrid_fitpack, _solve_2d_fitpack) by returning the residual matrix, avoiding deep copies in F.__call__, and adding an early exit in the knot-growth loop.</t>
         </is>
@@ -10139,13 +10935,18 @@
       <c r="K160" s="3" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M160" s="2" t="n">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N160" s="3" t="inlineStr">
+      <c r="O160" s="3" t="inlineStr">
         <is>
           <t>Adds the inverse of the digamma function as a new public function in scipy.special, previously only available as a private helper in stats.</t>
         </is>
@@ -10202,10 +11003,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M161" s="2" t="n">
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N161" s="3" t="inlineStr">
+      <c r="O161" s="3" t="inlineStr">
         <is>
           <t>Fixes the output shape of the Fiedler companion matrix for length-1 input to return a (0,0) matrix as documented, instead of a (0,) array.</t>
         </is>
@@ -10262,10 +11068,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M162" s="2" t="n">
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N162" s="3" t="inlineStr">
+      <c r="O162" s="3" t="inlineStr">
         <is>
           <t>Replaces the general LAPACK solver `dgesv` with the symmetric solver `dsysv` for the linear system in RBF interpolation; the mathematical output is unchanged but numerical stability and performance are improved.</t>
         </is>
@@ -10322,10 +11133,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M163" s="2" t="n">
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N163" s="3" t="inlineStr">
+      <c r="O163" s="3" t="inlineStr">
         <is>
           <t>Fixes incorrect status check and bracket attribute in mode calculation for univariate distributions, correcting edge case handling.</t>
         </is>
@@ -10382,10 +11198,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M164" s="2" t="n">
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N164" s="3" t="inlineStr">
+      <c r="O164" s="3" t="inlineStr">
         <is>
           <t>Fixes the return shape of the Fiedler matrix function for empty input to be (0,0) as documented, instead of the incorrect (0,).</t>
         </is>
@@ -10443,13 +11264,18 @@
       <c r="K165" s="3" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M165" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="N165" s="3" t="inlineStr">
+      <c r="O165" s="3" t="inlineStr">
         <is>
           <t>Replaced naive covariance/correlation computation with an incremental (online) algorithm to fix numerical instability.</t>
         </is>
@@ -10508,13 +11334,18 @@
       <c r="K166" s="3" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M166" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N166" s="3" t="inlineStr">
+      <c r="O166" s="3" t="inlineStr">
         <is>
           <t>Fixes wrong implementation of skewness and kurtosis by unifying online moment computation, handling degenerate distributions, and aligning results with SciPy.</t>
         </is>
@@ -10569,13 +11400,18 @@
       <c r="K167" s="3" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M167" s="2" t="n">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N167" s="3" t="inlineStr">
+      <c r="O167" s="3" t="inlineStr">
         <is>
           <t>Fixes `Timestamp.to_julian_date` to compute Julian date from UTC instant instead of local wall-clock time, affecting timezone-aware timestamps.</t>
         </is>

--- a/PRs.xlsx
+++ b/PRs.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All PRs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Repos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11526,4 +11527,221 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Repo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PR Number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Algorithm Name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Paper Reference</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Has Test</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Test Links</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Has Benchmark</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Bench Links</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Has Issue</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>AI Generated</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mdtraj/mdtraj</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>add formal charge in missing places on topology</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://github.com/mdtraj/mdtraj/pull/2038</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>fix_wrong_implementation</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Topology.join() formal charge propagation</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>tests/test_topology.py::test_topology_join_formal_charge</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Bug fix: formalCharge of metal ion is dropped when using Topology.join(); PR propagates the charge through copy() and add_atom().</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8957</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Modern stereo: fix stereo inversion in rings</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/8957</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>fix_wrong_implementation</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SMILES stereochemistry perception (CIP stereo in rings)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Code/GraphMol/catch_chirality.cpp</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Bug fix: modern stereo perception inverts atom parity in ring systems with multiple stereocenters; regression introduced by PR #8738 interacting with #1294.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>